--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92539875791</v>
+        <v>46157.93113873136</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113873136</v>
+        <v>46157.93368176754</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368176754</v>
+        <v>46157.93671858979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93671858979</v>
+        <v>46158.28194088231</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28194088231</v>
+        <v>46158.29718081476</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29718081476</v>
+        <v>46158.29790256047</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29790256047</v>
+        <v>46158.33355740747</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355740747</v>
+        <v>46158.37210648603</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210648603</v>
+        <v>46158.37267660591</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
